--- a/artfynd/A 61749-2021 artfynd.xlsx
+++ b/artfynd/A 61749-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116992928</v>
+        <v>116992925</v>
       </c>
       <c r="B2" t="n">
-        <v>90452</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494974</v>
+        <v>495549</v>
       </c>
       <c r="R2" t="n">
-        <v>7073275</v>
+        <v>7073207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116992950</v>
+        <v>116992938</v>
       </c>
       <c r="B3" t="n">
-        <v>90470</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495198</v>
+        <v>495094</v>
       </c>
       <c r="R3" t="n">
-        <v>7073418</v>
+        <v>7072932</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116992939</v>
+        <v>116992949</v>
       </c>
       <c r="B4" t="n">
-        <v>91768</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5448</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495054</v>
+        <v>495549</v>
       </c>
       <c r="R4" t="n">
-        <v>7073335</v>
+        <v>7073206</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116992929</v>
+        <v>116992928</v>
       </c>
       <c r="B5" t="n">
-        <v>90470</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494942</v>
+        <v>494974</v>
       </c>
       <c r="R5" t="n">
-        <v>7073099</v>
+        <v>7073275</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116992922</v>
+        <v>116992932</v>
       </c>
       <c r="B6" t="n">
-        <v>90470</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495193</v>
+        <v>495543</v>
       </c>
       <c r="R6" t="n">
-        <v>7072945</v>
+        <v>7073204</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116992947</v>
+        <v>116992927</v>
       </c>
       <c r="B7" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495184</v>
+        <v>495404</v>
       </c>
       <c r="R7" t="n">
-        <v>7073467</v>
+        <v>7073290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,37 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116992925</v>
+        <v>116992923</v>
       </c>
       <c r="B8" t="n">
-        <v>90399</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>4405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495549</v>
+        <v>495162</v>
       </c>
       <c r="R8" t="n">
-        <v>7073207</v>
+        <v>7073468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116992938</v>
+        <v>116992939</v>
       </c>
       <c r="B9" t="n">
-        <v>86772</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495094</v>
+        <v>495054</v>
       </c>
       <c r="R9" t="n">
-        <v>7072932</v>
+        <v>7073335</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116992932</v>
+        <v>116992947</v>
       </c>
       <c r="B10" t="n">
-        <v>90452</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495543</v>
+        <v>495184</v>
       </c>
       <c r="R10" t="n">
-        <v>7073204</v>
+        <v>7073467</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,6 +1556,11 @@
           <t>2023-10-03</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1627,536 +1582,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>116992952</v>
-      </c>
-      <c r="B11" t="n">
-        <v>90470</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Kojflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>495408</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7073325</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>116992949</v>
-      </c>
-      <c r="B12" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>658</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Kojflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>495549</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7073206</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>116992923</v>
-      </c>
-      <c r="B13" t="n">
-        <v>87286</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>4405</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Diskvaxskivling</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Hygrophorus discoideus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Pers.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Kojflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>495162</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7073468</v>
-      </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>116992927</v>
-      </c>
-      <c r="B14" t="n">
-        <v>91737</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>4366</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Skarp dropptaggsvamp</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Hydnellum peckii</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Kojflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>495404</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7073290</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>116992951</v>
-      </c>
-      <c r="B15" t="n">
-        <v>90470</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Kojflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>495254</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7073379</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2023-10-03</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Pär Hedberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2023</t>
         </is>
